--- a/questionnaire_templates/027_creative_direction_self_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/027_creative_direction_self_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your name?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,30 +604,30 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>work_approach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Work approach</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,58 +639,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>main_goals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Main goals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what_are_your_goals</t>
+          <t>values</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are your goals?</t>
+          <t>Values</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>how_do_you_approach</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How do you approach your work?</t>
+          <t>Time management skills</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_do_you_value</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What do you value most?</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,368 +726,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Communication skills</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time management skills?</t>
+          <t>Adaptability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>what_is_your_work_style</t>
+          <t>final_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your work style?</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>what_do_you_value_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What do you value 2?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>what_do_you_do</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What do you do?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Communication skills?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>what_do_you_value_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What do you value 3?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What do you value 4?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>what_is_your_work_style_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is your work style?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>time_management_skills</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Time management skills?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What do you value 5?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>what_is_your_work_style_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your work style?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>what_do_you_do_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What do you do?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>team_work</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Teamwork?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Time management skills?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What do you value 6?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +803,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1211,323 +916,323 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>work_approach_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>creativity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Creativity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>work_approach_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Efficiency</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>work_approach_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>joe</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manager_choices</t>
+          <t>work_approach_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mary</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Effectiveness</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_do_you_approach_choices</t>
+          <t>work_approach_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>creativity</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Creativity</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_do_you_approach_choices</t>
+          <t>main_goals_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Innovation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_do_you_approach_choices</t>
+          <t>main_goals_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>originality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Originality</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_do_you_approach_choices</t>
+          <t>main_goals_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>effectiveness</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Effectiveness</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>how_do_you_approach_choices</t>
+          <t>main_goals_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>timeliness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Timeliness</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>what_do_you_value_choices</t>
+          <t>main_goals_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>innovation</t>
+          <t>creativity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Creativity</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>what_do_you_value_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>originality</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Originality</t>
+          <t>Innovation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>what_do_you_value_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>originality</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Originality</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>what_do_you_value_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>timeliness</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>what_do_you_value_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>creativity</t>
+          <t>timeliness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Creativity</t>
+          <t>Timeliness</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>what_do_you_value_2_choices</t>
+          <t>values_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>what_do_you_value_2_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>verbal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Verbal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>what_do_you_value_2_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>non-verbal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Non-Verbal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>what_do_you_value_2_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>written</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>what_do_you_value_2_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>verbal_and_non-verbal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Verbal and Non-Verbal</t>
         </is>
       </c>
     </row>
@@ -1539,505 +1244,97 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>verbal</t>
+          <t>verbal_and_written</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Verbal and Written</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>adaptability_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>non-verbal</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Non-Verbal</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>adaptability_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>written</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>adaptability_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>verbal_and_non-verbal</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verbal and Non-Verbal</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>adaptability_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>verbal_and_written</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verbal and Written</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>what_do_you_value_3_choices</t>
+          <t>adaptability_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>what_do_you_value_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>what_do_you_value_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>what_do_you_value_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>what_do_you_value_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>what_do_you_value_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>originality</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Originality</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>what_do_you_value_5_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>team_work_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>collaborative</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Collaborative</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>team_work_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>individual</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>team_work_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>team_player</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Team Player</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>team_work_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>team_manager</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Team Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>team_work_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>team_leader</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Team Leader</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>what_do_you_value_6_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Leadership</t>
         </is>
       </c>
     </row>
